--- a/Result/profitability/8027.xlsx
+++ b/Result/profitability/8027.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.22375</v>
+        <v>-0.20625</v>
       </c>
       <c r="N2" t="n">
-        <v>33.0725</v>
+        <v>32.56625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-3.35</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.595</v>
+        <v>-0.60625</v>
       </c>
       <c r="N3" t="n">
-        <v>31.92125</v>
+        <v>30.87</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-3.04</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.95625</v>
+        <v>-0.915</v>
       </c>
       <c r="N4" t="n">
-        <v>29.28</v>
+        <v>29.06</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.09</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.14625</v>
+        <v>-1.035</v>
       </c>
       <c r="N5" t="n">
-        <v>28.31625</v>
+        <v>27.52</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>2.04</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.75</v>
+        <v>-0.7949999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>26.9575</v>
+        <v>26.09</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7025000000000001</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>25.4725</v>
+        <v>24.73625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8429,6 +8429,133 @@
       </c>
       <c r="AM63" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>8027</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>627</v>
+      </c>
+      <c r="D64" t="n">
+        <v>441</v>
+      </c>
+      <c r="E64" t="n">
+        <v>186</v>
+      </c>
+      <c r="F64" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-3.06%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-29</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-0.23875</v>
+      </c>
+      <c r="N64" t="n">
+        <v>33.91</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-0.01999999999999999</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0.09090909090909083</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-0.01999999999999957</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-0.0006722689075630006</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>-0.7876106194690266</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>-6.370000000000001</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>-0.1764542936288089</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
